--- a/test/appium_tests/result/result_register.xlsx
+++ b/test/appium_tests/result/result_register.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,6 +520,433 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0339420357</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>blackoden@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>123456</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lỗi: ❌ Không thể nhập First Name sau 5 lần thử.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-04-22 03:51:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Test 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0339420357</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>blackoden@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>123456</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Đăng ký hoặc đăng nhập không thành công: Exception: Đăng ký không thành công</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-04-22 04:08:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Test 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Khai</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0339420358</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>blackoden@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>123456</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Đăng ký hoặc đăng nhập không thành công: Exception: Đăng ký không thành công</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-04-22 04:08:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Khai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>blackoden@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>123456</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Đăng ký hoặc đăng nhập không thành công: Exception: Đăng ký không thành công</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-04-22 04:09:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Test 4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Khai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0339420360</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>123456</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Đăng ký hoặc đăng nhập không thành công: Exception: Đăng ký không thành công</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-04-22 04:10:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Test 5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Khai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0339420361</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>blackoden@gmail.com</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Đăng ký hoặc đăng nhập không thành công: Exception: Đăng ký không thành công</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2025-04-22 04:11:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Test 6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Khai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0339420362</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>khai@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>123456</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Đăng ký hoặc đăng nhập không thành công: Exception: Đăng ký không thành công</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2025-04-22 04:12:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Test 7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Khai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0339420356</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>blackoden@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>123456</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Đăng ký hoặc đăng nhập không thành công: Exception: Đăng ký không thành công</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025-04-22 04:12:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Test 8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Khai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>123</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>blackoden@gmail.com</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>123456</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thành Công</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2025-04-22 04:13:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Test 9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Khai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0339420354</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>blackoden.com</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>123456</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lỗi: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the page using the given search parameters.
+    at AndroidUiautomator2Driver.findElOrEls (C:\Users\ADMIN\AppData\Local\Programs\Appium Server GUI\resources\app\node_modules\appium\node_modules\appium-android-driver\lib\commands\find.js:75:11)
+    at runMicrotasks (&lt;anonymous&gt;)
+    at processTicksAndRejections (internal/process/task_queues.js:97:5)
+    at AndroidUiautomator2Driver.findElOrElsWithProcessing (C:\Users\ADMIN\AppData\Local\Programs\Appium Server GUI\resources\app\node_modules\appium\node_modules\appium-base-driver\lib\basedriver\commands\find.js:33:12)
+    at AndroidUiautomator2Driver.findElement (C:\Users\ADMIN\AppData\Local\Programs\Appium Server GUI\resources\app\node_modules\appium\node_modules\appium-base-driver\lib\basedriver\commands\find.js:53:10)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025-04-22 04:14:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
